--- a/uat/inputs/ethnic_wear_structural.xlsx
+++ b/uat/inputs/ethnic_wear_structural.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>model_code_input_data</t>
+          <t>input_data</t>
         </is>
       </c>
     </row>
